--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260810.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260810.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>144,685</t>
+          <t>138,585</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>30.02%</t>
+          <t>29.86%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>16,485</t>
+          <t>15,785</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.91%</t>
+          <t>7.97%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>104,820</t>
+          <t>100,320</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.47%</t>
+          <t>7.72%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>53,365</t>
+          <t>51,065</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.66%</t>
+          <t>5.43%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>127,295</t>
+          <t>121,895</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.22%</t>
+          <t>5.26%</t>
         </is>
       </c>
     </row>
@@ -721,78 +721,78 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>62,630</t>
+          <t>59,930</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.79%</t>
+          <t>3.89%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>SO US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>68,835</t>
+          <t>7,486,042</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.82%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>EQIX US</t>
+          <t>SO US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Equinix公司</t>
+          <t>南方公司</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>5,985</t>
+          <t>65,935</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.07%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>EQIX US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>Equinix公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>47,365</t>
+          <t>5,685</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>3.02%</t>
         </is>
       </c>
     </row>
@@ -809,183 +809,183 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>19,173</t>
+          <t>18,373</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.91%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>20,725</t>
+          <t>45,365</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.80%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>180,043,801</t>
+          <t>19,825</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.73%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>慧與</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>80,705</t>
+          <t>160,671,600</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>AEP US</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>美國電力公司</t>
+          <t>慧與</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>33,160</t>
+          <t>77,305</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.15%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>DLR US</t>
+          <t>AEP US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>數位不動產信託公司</t>
+          <t>美國電力公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>21,295</t>
+          <t>31,760</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>DLR US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>數位不動產信託公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>53,645</t>
+          <t>20,395</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>27,858</t>
+          <t>51,345</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.76%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>38,000</t>
+          <t>26,658</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,149 +997,149 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>20,430</t>
+          <t>36,400</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>愛克斯龍公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>62,248</t>
+          <t>19,530</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>愛克斯龍公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>8,390</t>
+          <t>59,648</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.35%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>10,036</t>
+          <t>7,990</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>22,308</t>
+          <t>9,636</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>133,375</t>
+          <t>21,408</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>12,201</t>
+          <t>127,675</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,88 +1151,88 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>19,255</t>
+          <t>11,701</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>20,517</t>
+          <t>18,455</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>16,571</t>
+          <t>19,617</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>39,390</t>
+          <t>15,871</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>45,390</t>
+          <t>43,490</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,22 +1261,22 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,529,083</t>
+          <t>37,690</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>12,265</t>
+          <t>11,765</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>219,477,900</t>
+          <t>483,561,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>6,456,960</t>
+          <t>8,679,840</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
